--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/aysen.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/aysen.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>14442.5</v>
+        <v>14430.89</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>17248.18</v>
+        <v>17223.98</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>21179.18</v>
+        <v>21324.96</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>12721.66</v>
+        <v>12702.95</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>8636.940000000001</v>
+        <v>8599.73</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>13623.68</v>
+        <v>13666.54</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>16441.35</v>
+        <v>16493.08</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>14954.25</v>
+        <v>14888.7</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>13001.7</v>
+        <v>13043.08</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>6508.93</v>
+        <v>6585.28</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>32212.41</v>
+        <v>32590.28</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>51556.72</v>
+        <v>51420.35</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>30718.59</v>
+        <v>30657.01</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/aysen.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,22 +514,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>886182-300-CM25</t>
+          <t>418-2288-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Universidad de Aysen</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>GLOMAX S.A.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>76.817.867-4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>14430.89</v>
+        <v>11086.61</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1095439-18-CM25</t>
+          <t>886182-300-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>72.222.000-5</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE AYSEN</t>
+          <t>Universidad de Aysen</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>17223.98</v>
+        <v>14430.89</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1494998-5-CM25</t>
+          <t>1095439-18-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>72.222.000-5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>GOBIERNO REGIONAL DE AYSEN</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>21324.96</v>
+        <v>17223.98</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1233615-74-CM26</t>
+          <t>1494998-5-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>FAST OFFICE LIMITADA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77.205.938-8</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>12702.95</v>
+        <v>21324.96</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1691-595-CM26</t>
+          <t>1233615-74-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>FAST OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.205.938-8</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>8599.73</v>
+        <v>12702.95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4679-35-CM26</t>
+          <t>1691-595-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>13666.54</v>
+        <v>8599.73</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1182705-86-CM26</t>
+          <t>4679-35-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -900,17 +900,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>65.199.131-5</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACIÓN TÉCNICA DE LA REGIÓN DE AYSÉN DEL GENERAL CARLOS I</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>16493.08</v>
+        <v>13666.54</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1233615-794-CM26</t>
+          <t>1182705-86-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>65.199.131-5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA DE LA REGIÓN DE AYSÉN DEL GENERAL CARLOS I</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>LOYDA EUGENIA HENRÍQUEZ ORELLANA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>11.216.890-7</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>14888.7</v>
+        <v>16493.08</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1426103-41-CM26</t>
+          <t>1233615-794-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>LOYDA EUGENIA HENRÍQUEZ ORELLANA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>11.216.890-7</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>13043.08</v>
+        <v>14888.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>886182-167-CM26</t>
+          <t>1426103-41-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,27 +1073,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Universidad de Aysen</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>6585.28</v>
+        <v>13043.08</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>868-79-CM26</t>
+          <t>886182-167-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1144,17 +1144,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>72.222.000-5</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE AYSEN</t>
+          <t>Universidad de Aysen</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>32590.28</v>
+        <v>6585.28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1233615-938-CM26</t>
+          <t>868-79-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>72.222.000-5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>GOBIERNO REGIONAL DE AYSEN</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.043.435-1</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>51420.35</v>
+        <v>32590.28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4679-58-CM26</t>
+          <t>1233615-938-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,27 +1256,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>77.043.435-1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,6 +1301,67 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
+        <v>51420.35</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>4679-58-CM26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>61.104.000-8</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
         <v>30657.01</v>
       </c>
     </row>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/aysen.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/aysen.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aysén" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Aysén" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>418-2288-CM25</t>
+          <t>1233615-472-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>GLOMAX S.A.</t>
+          <t>OFISILLAS CHILE SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.817.867-4</t>
+          <t>76.855.435-8</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,28 +569,28 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>11086.61</v>
+        <v>11602.34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>886182-300-CM25</t>
+          <t>1426103-117-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Universidad de Aysen</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>Ortopedic</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>77.765.630-9</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,28 +630,28 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>14430.89</v>
+        <v>5876.56</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1095439-18-CM25</t>
+          <t>1057062-200-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>72.222.000-5</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE AYSEN</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,28 +691,28 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>17223.98</v>
+        <v>25314.02</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1494998-5-CM25</t>
+          <t>1057062-226-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,43 +752,43 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>21324.96</v>
+        <v>13255.47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1233615-74-CM26</t>
+          <t>2182-100-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>FAST OFFICE LIMITADA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>77.205.938-8</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,28 +813,28 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>12702.95</v>
+        <v>28416.68</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1691-595-CM26</t>
+          <t>2713-662-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,43 +874,43 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>8599.73</v>
+        <v>5810.59</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4679-35-CM26</t>
+          <t>868-159-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>72.222.000-5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>GOBIERNO REGIONAL DE AYSEN</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,28 +935,28 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>13666.54</v>
+        <v>6514.24</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1182705-86-CM26</t>
+          <t>418-2288-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2239-4-LR25</t>
+          <t>2239-3-LR23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>65.199.131-5</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACIÓN TÉCNICA DE LA REGIÓN DE AYSÉN DEL GENERAL CARLOS I</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>GLOMAX S.A.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>76.817.867-4</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>16493.08</v>
+        <v>11086.61</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1233615-794-CM26</t>
+          <t>886182-300-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>Universidad de Aysen</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>LOYDA EUGENIA HENRÍQUEZ ORELLANA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>11.216.890-7</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>14888.7</v>
+        <v>14430.89</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1426103-41-CM26</t>
+          <t>1095439-18-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>72.222.000-5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>GOBIERNO REGIONAL DE AYSEN</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>13043.08</v>
+        <v>17223.98</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>886182-167-CM26</t>
+          <t>1494998-5-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,27 +1134,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Universidad de Aysen</t>
+          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>6585.28</v>
+        <v>21324.96</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>868-79-CM26</t>
+          <t>1233615-74-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>72.222.000-5</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE AYSEN</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>FAST OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>77.205.938-8</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>32590.28</v>
+        <v>12702.95</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1233615-938-CM26</t>
+          <t>1691-595-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.043.435-1</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>51420.35</v>
+        <v>8599.73</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>4679-58-CM26</t>
+          <t>4679-35-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,6 +1362,433 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
+        <v>13666.54</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1182705-86-CM26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>65.199.131-5</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>CENTRO DE FORMACIÓN TÉCNICA DE LA REGIÓN DE AYSÉN DEL GENERAL CARLOS I</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>STATUS SPA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>16493.08</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1233615-794-CM26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>61.980.950-5</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Aysén</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>LOYDA EUGENIA HENRÍQUEZ ORELLANA</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>11.216.890-7</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>14888.7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1426103-41-CM26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>13043.08</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>886182-167-CM26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>61.980.520-8</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Universidad de Aysen</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>6585.28</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>868-79-CM26</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>72.222.000-5</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>STATUS SPA</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>77.393.671-4</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>32590.28</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1233615-938-CM26</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>61.980.950-5</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Aysén</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>MUEBLES CAMILA GALLEGUILLOS E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>77.043.435-1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>51420.35</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>4679-58-CM26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>61.104.000-8</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>LEFI SPA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>77.324.357-3</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
         <v>30657.01</v>
       </c>
     </row>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/aysen.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/aysen.xlsx
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Universidad de Aysen</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Universidad de Aysen</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/aysen.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/aysen.xlsx
@@ -562,7 +562,11 @@
           <t>76.855.435-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +948,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1074,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1139,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1204,11 @@
           <t>96.882.140-7</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1330,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1395,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1460,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1586,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1651,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1716,11 @@
           <t>77.393.671-4</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1781,11 @@
           <t>77.043.435-1</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1846,11 @@
           <t>77.324.357-3</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/aysen.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1860,6 +1860,71 @@
         <v>30657.01</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>4679-80-CM26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-4-LR25</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>61.104.000-8</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>COMERCIAL E INDUSTRIAL MUEBLES ASENJO LIMITADA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>77.018.060-0</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>6823.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/oc-regiones/mobiliario-general-escolar-y-clinico/aysen.xlsx
+++ b/docs/oc-regiones/mobiliario-general-escolar-y-clinico/aysen.xlsx
@@ -1623,7 +1623,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
